--- a/routing/taskana-routing-rest/src/test/resources/testExcelRoutingWithInvalidOutputs.xlsx
+++ b/routing/taskana-routing-rest/src/test/resources/testExcelRoutingWithInvalidOutputs.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24617"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D57D6153-B6DF-40DC-8B57-04DC677C69EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{86DC1A7C-DB2B-47B9-A627-CDF0567DBE38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="5790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -93,7 +93,7 @@
     <t>12345678</t>
   </si>
   <si>
-    <t>GPK_KSC2</t>
+    <t>DOMAIN_XZ</t>
   </si>
 </sst>
 </file>
@@ -635,10 +635,10 @@
         <v>20</v>
       </c>
       <c r="D8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" t="s">
         <v>21</v>
-      </c>
-      <c r="E8" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
